--- a/data/trans_orig/P79A2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A2_2023-Provincia-trans_orig.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>704</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,27 +2440,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,27 +3126,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>34491</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3161,27 +3161,27 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>28202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>48593</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>68175</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>68957</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>68957</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>68957</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>39613</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65387</t>
+          <t>90492</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>116904</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
